--- a/trading_signals/risk_management/risk_workbook_20260617_000000.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260617_000000.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -147,10 +147,10 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,22 +184,22 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,12 +212,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -357,12 +351,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'NAV Trend'!$A$4:$A$160</f>
+              <f>'NAV Trend'!$A$4:$A$159</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'NAV Trend'!$B$4:$B$160</f>
+              <f>'NAV Trend'!$B$4:$B$159</f>
             </numRef>
           </val>
         </ser>
@@ -734,7 +728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-17  ·  Generated 2026-06-24T21:36:52  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-16  ·  Generated 2026-06-25T01:50:06  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -745,7 +739,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
     </row>
     <row r="5">
@@ -755,7 +749,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.919</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="6">
@@ -764,8 +758,8 @@
           <t>Net leverage (x)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>0.355</v>
+      <c r="B6" s="6" t="n">
+        <v>0.431</v>
       </c>
     </row>
     <row r="7">
@@ -774,8 +768,8 @@
           <t>Net market beta (target≈0)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>1.022</v>
+      <c r="B7" s="5" t="n">
+        <v>1.321</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +779,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22944.33</v>
+        <v>29530.01</v>
       </c>
     </row>
     <row r="9">
@@ -794,8 +788,8 @@
           <t>VaR 95% 1-day (% NAV)</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>2.04</v>
+      <c r="B9" s="5" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="10">
@@ -804,8 +798,8 @@
           <t>Annual vol (% NAV)</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>19.66</v>
+      <c r="B10" s="5" t="n">
+        <v>25.42</v>
       </c>
     </row>
     <row r="11">
@@ -814,8 +808,8 @@
           <t>Sharpe (annual)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>1.445</v>
+      <c r="B11" s="5" t="n">
+        <v>1.42</v>
       </c>
     </row>
     <row r="12">
@@ -824,8 +818,8 @@
           <t>PSR( SR&gt;0 )</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>0.8747</v>
+      <c r="B12" s="6" t="n">
+        <v>0.8699</v>
       </c>
     </row>
     <row r="13">
@@ -834,7 +828,7 @@
           <t>CDaR 95% (%)</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="5" t="n">
         <v>8.859999999999999</v>
       </c>
     </row>
@@ -846,7 +840,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>5.07 / 2.54</t>
+          <t>4.96 / 2.48</t>
         </is>
       </c>
     </row>
@@ -857,7 +851,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.919</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="16">
@@ -868,7 +862,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>AMAT (16.27% NAV)</t>
+          <t>KLAC (24.13% NAV)</t>
         </is>
       </c>
     </row>
@@ -878,8 +872,8 @@
           <t>Max sector net (% gross)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>38.19</v>
+      <c r="B17" s="5" t="n">
+        <v>37.79</v>
       </c>
     </row>
     <row r="18">
@@ -888,8 +882,8 @@
           <t>Open pairs</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>6</v>
+      <c r="B18" s="5" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -898,8 +892,8 @@
           <t>Limit breaches</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>5</v>
+      <c r="B19" s="5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -928,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -950,7 +944,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>22944.33</v>
+        <v>29530.01</v>
       </c>
     </row>
     <row r="4">
@@ -960,7 +954,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>32442.87</v>
+        <v>41754.9</v>
       </c>
     </row>
     <row r="5">
@@ -970,7 +964,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>221416.41</v>
+        <v>284969.25</v>
       </c>
     </row>
     <row r="6">
@@ -979,8 +973,8 @@
           <t>Annual vol (% NAV)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>19.66</v>
+      <c r="B6" s="5" t="n">
+        <v>25.42</v>
       </c>
     </row>
     <row r="7">
@@ -990,7 +984,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11738.61</v>
+        <v>16119.33</v>
       </c>
     </row>
     <row r="8">
@@ -1000,11 +994,11 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22781.28</v>
+        <v>30116.89</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>COMPONENT VaR (per pair, marginal)</t>
         </is>
@@ -1034,10 +1028,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>7731.48</v>
+        <v>7460.3</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>33.7</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="13">
@@ -1047,62 +1041,75 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>7588.85</v>
+        <v>7456.14</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>33.08</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3851.06</v>
+        <v>5492.5</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>16.78</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2033.88</v>
+        <v>3729.93</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>8.859999999999999</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1638.78</v>
+        <v>2051.05</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>7.14</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>100.28</v>
+        <v>1687.49</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>0.44</v>
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>STLD/UHS</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>1652.61</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1173,19 +1180,19 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>578</v>
+        <v>670</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1132306</v>
+        <v>5871551</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -1194,19 +1201,19 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>3311</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>5226987</v>
+        <v>1100599</v>
       </c>
       <c r="E7" s="16" t="n">
         <v>0</v>
@@ -1215,19 +1222,19 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>670</v>
+        <v>329</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6476364</v>
+        <v>1470419</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1236,19 +1243,19 @@
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>23</v>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>422</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>1127224</v>
+        <v>750048</v>
       </c>
       <c r="E9" s="16" t="n">
         <v>0</v>
@@ -1269,7 +1276,7 @@
         <v>386</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1125856</v>
+        <v>1131108</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1290,7 +1297,7 @@
         <v>358</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1002137</v>
+        <v>999944</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>0</v>
@@ -1299,19 +1306,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>309</v>
+        <v>470</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8835886</v>
+        <v>5871551</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1325,14 +1332,14 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>1466</v>
+        <v>972</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>2904350</v>
+        <v>2889043</v>
       </c>
       <c r="E13" s="16" t="n">
         <v>0</v>
@@ -1341,19 +1348,19 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>10458954</v>
+        <v>8711508</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1362,19 +1369,19 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>395</v>
+        <v>1466</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>2402636</v>
+        <v>2889043</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>0</v>
@@ -1383,19 +1390,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1936716</v>
+        <v>10234157</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1404,21 +1411,63 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>395</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>2478671</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>ODFL/PLTR</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>394</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1912590</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C19" s="12" t="n">
         <v>372</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>38900737</v>
-      </c>
-      <c r="E17" s="16" t="n">
+      <c r="D19" s="12" t="n">
+        <v>38774742</v>
+      </c>
+      <c r="E19" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1474,11 +1523,11 @@
           <t>SPY -5%</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n">
-        <v>-57542.9</v>
-      </c>
-      <c r="C4" s="21" t="n">
-        <v>-5.11</v>
+      <c r="B4" s="18" t="n">
+        <v>-74044.83</v>
+      </c>
+      <c r="C4" s="22" t="n">
+        <v>-6.61</v>
       </c>
     </row>
     <row r="5">
@@ -1487,11 +1536,11 @@
           <t>SPY -10%</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
-        <v>-115085.8</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <v>-10.22</v>
+      <c r="B5" s="19" t="n">
+        <v>-148089.67</v>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>-13.21</v>
       </c>
     </row>
     <row r="6">
@@ -1500,11 +1549,11 @@
           <t>VIX +10pt</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
-        <v>-57542.9</v>
-      </c>
-      <c r="C6" s="21" t="n">
-        <v>-5.11</v>
+      <c r="B6" s="18" t="n">
+        <v>-74044.83</v>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>-6.61</v>
       </c>
     </row>
     <row r="7">
@@ -1513,11 +1562,11 @@
           <t>Top sector -10%</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
-        <v>-39522.14</v>
-      </c>
-      <c r="C7" s="23" t="n">
-        <v>-3.51</v>
+      <c r="B7" s="19" t="n">
+        <v>-44318.3</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>-3.95</v>
       </c>
     </row>
   </sheetData>
@@ -1585,130 +1634,130 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>gross_leverage</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>mrpt</t>
         </is>
       </c>
-      <c r="C4" s="32" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="D4" s="32" t="n">
+      <c r="C4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="32" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>net_leverage_abs</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>mrpt</t>
         </is>
       </c>
-      <c r="C5" s="32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D5" s="32" t="n">
+      <c r="C5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="32" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>gross_leverage</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>mtfs</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="D6" s="32" t="n">
+      <c r="C6" s="30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="D6" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="32" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>net_leverage_abs</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>mtfs</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="D7" s="34" t="n">
+      <c r="C7" s="32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D7" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="34" t="n">
+      <c r="E7" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="32" t="inlineStr">
         <is>
           <t>amber</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>single_name_gross</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="D8" s="34" t="n">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="D8" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="34" t="n">
+      <c r="E8" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="34" t="inlineStr">
+      <c r="F8" s="32" t="inlineStr">
         <is>
           <t>amber</t>
         </is>
@@ -1722,11 +1771,11 @@
       </c>
       <c r="B9" s="32" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>14.2</v>
+        <v>15.66</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1736,183 +1785,183 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>single_name_gross</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="30" t="inlineStr">
+        <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
-        <is>
-          <t>single_name_gross</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>STLD</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="E10" s="32" t="n">
-        <v>25</v>
-      </c>
-      <c r="F10" s="32" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>sector_net</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>max_pair</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>amber</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>net_market_beta</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>var_95_1d</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>combined</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>sector_net</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>38.19</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <v>50</v>
-      </c>
-      <c r="F11" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>max_pair</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="n">
-        <v>24.63</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <v>35</v>
-      </c>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>amber</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>net_market_beta</t>
-        </is>
-      </c>
-      <c r="B13" s="36" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
-        <is>
-          <t>var_95_1d</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>combined</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="D14" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="32" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>open_pairs</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>mrpt</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>open_pairs</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
-        <is>
-          <t>mrpt</t>
-        </is>
-      </c>
-      <c r="C15" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="32" t="n">
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>mtfs</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="31" t="inlineStr">
-        <is>
-          <t>open_pairs</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>mtfs</t>
-        </is>
-      </c>
-      <c r="C16" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="inlineStr">
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>green</t>
         </is>
@@ -1932,7 +1981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2009,17 +2058,17 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
@@ -2028,17 +2077,17 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>578</v>
+        <v>670</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>143.92</v>
+        <v>237.33</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>83185.75999999999</v>
+        <v>159011.1</v>
       </c>
       <c r="H4" s="16" t="inlineStr">
         <is>
-          <t>realestate</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I4" s="16" t="n">
@@ -2046,24 +2095,24 @@
       </c>
       <c r="J4" s="16" t="inlineStr">
         <is>
-          <t>slow_signal</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2072,17 +2121,17 @@
         </is>
       </c>
       <c r="E5" s="24" t="n">
-        <v>-3311</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>24.33</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>-80556.63</v>
+        <v>-23</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>614.73</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>-14138.79</v>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
@@ -2090,7 +2139,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>slow_signal</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2151,12 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -2116,17 +2165,17 @@
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>670</v>
+        <v>329</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>238.73</v>
+        <v>259.08</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>159949.1</v>
+        <v>85237.32000000001</v>
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="I6" s="16" t="n">
@@ -2134,7 +2183,7 @@
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2146,12 +2195,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2160,17 +2209,17 @@
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-23</v>
+        <v>-422</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>607.9299999999999</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>-13982.39</v>
+        <v>124.81</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-52669.82</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -2178,7 +2227,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2207,10 +2256,10 @@
         <v>386</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>270.13</v>
+        <v>274.29</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>104270.18</v>
+        <v>105875.94</v>
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
@@ -2251,10 +2300,10 @@
         <v>-358</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>141.26</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>-50571.08</v>
+        <v>146.9</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>-52590.2</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -2278,12 +2327,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -2292,13 +2341,13 @@
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>309</v>
+        <v>470</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>592.92</v>
+        <v>237.33</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>183212.28</v>
+        <v>111545.1</v>
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
@@ -2306,11 +2355,11 @@
         </is>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2371,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -2336,13 +2385,13 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-1466</v>
+        <v>-972</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>-71643.42</v>
+        <v>50.78</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>-49358.16</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -2350,11 +2399,11 @@
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2415,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
@@ -2380,13 +2429,13 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>374.18</v>
+        <v>568.23</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>100654.42</v>
+        <v>175583.07</v>
       </c>
       <c r="H12" s="16" t="inlineStr">
         <is>
@@ -2398,7 +2447,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2459,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>AMAT/TRMB</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2424,17 +2473,17 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-395</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>132.13</v>
-      </c>
-      <c r="G13" s="28" t="n">
-        <v>-52191.35</v>
+        <v>-1466</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>-74443.48</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
@@ -2442,7 +2491,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2503,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
@@ -2468,17 +2517,17 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>394</v>
+        <v>269</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>218.36</v>
+        <v>369.08</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>86033.84</v>
+        <v>99282.52</v>
       </c>
       <c r="H14" s="16" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I14" s="16" t="n">
@@ -2486,7 +2535,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>let_profits_run</t>
         </is>
       </c>
     </row>
@@ -2498,37 +2547,125 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-395</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>-52179.5</v>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>utilities</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>let_profits_run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>ODFL</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>394</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>231.62</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>91258.28</v>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>weekly_aligned_windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>ODFL/PLTR</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
+      <c r="E17" s="24" t="n">
         <v>-372</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>130.63</v>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>-48594.36</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="F17" s="4" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>-49569</v>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>tech</t>
         </is>
       </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
@@ -2548,7 +2685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2607,26 +2744,26 @@
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>89.62</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>24705.44</v>
       </c>
       <c r="D4" s="12" t="n">
-        <v>163742.39</v>
+        <v>173149.89</v>
       </c>
       <c r="E4" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>slow_signal</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
       <c r="G4" s="16" t="inlineStr">
@@ -2643,21 +2780,21 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>25799.84</v>
+        <v>5194.38</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>173931.49</v>
+        <v>137907.14</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -2678,10 +2815,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>1957.36</v>
+        <v>1544</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>154841.26</v>
+        <v>158466.14</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>1</v>
@@ -2705,21 +2842,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>AMAT/TRMB</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14103.1</v>
+        <v>13103.95</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>254855.7</v>
+        <v>160903.26</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -2736,21 +2873,21 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n">
-        <v>-193.31</v>
+          <t>AMAT/TRMB</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>3673.83</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>152845.77</v>
+        <v>250026.55</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>let_profits_run</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -2767,24 +2904,55 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
+          <t>LRCX/NRG</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>-1553.36</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>151462.02</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>let_profits_run</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
           <t>ODFL/PLTR</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
-        <v>-11416.2</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>134628.2</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="C10" s="19" t="n">
+        <v>-7166.4</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>140827.28</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>weekly_aligned_windows</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -2844,12 +3012,12 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -2861,12 +3029,12 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -2878,12 +3046,12 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -2895,12 +3063,12 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +3086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2943,7 +3111,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>MASTER (4 strategies) — 等资本 vs 等风险</t>
         </is>
@@ -2983,16 +3151,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.44</v>
+        <v>14.38</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.33</v>
+        <v>0.45</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="21" t="n">
-        <v>-14.11</v>
+      <c r="E6" s="22" t="n">
+        <v>-13.93</v>
       </c>
     </row>
     <row r="7">
@@ -3002,16 +3170,16 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>13.87</v>
+        <v>13.86</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>25.68</v>
+        <v>25.79</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <v>11.81</v>
+      <c r="E7" s="21" t="n">
+        <v>11.93</v>
       </c>
     </row>
     <row r="8">
@@ -3021,16 +3189,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>24.16</v>
+        <v>24.59</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>-20.6</v>
+      <c r="E8" s="22" t="n">
+        <v>-21.05</v>
       </c>
     </row>
     <row r="9">
@@ -3040,20 +3208,20 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>47.53</v>
+        <v>47.17</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>70.43000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <v>22.9</v>
+      <c r="E9" s="21" t="n">
+        <v>23.05</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>PAIRS (within combined book)</t>
         </is>
@@ -3078,7 +3246,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>33.7</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="14">
@@ -3088,47 +3256,57 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>33.08</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>LRCX/NRG</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>16.78</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>ODFL/PLTR</t>
+          <t>LRCX/NRG</t>
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>8.859999999999999</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>ODFL/PLTR</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>7.14</v>
+        <v>6.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>EXR/WY</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
-        <v>0.44</v>
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>STLD/UHS</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -3238,7 +3416,7 @@
           <t>COMBINED</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="23" t="n">
         <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
@@ -3287,7 +3465,7 @@
           <t>MRPT</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>47.74</v>
       </c>
       <c r="C6" s="16" t="n">
@@ -3336,7 +3514,7 @@
           <t>MTFS</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="23" t="n">
         <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
@@ -3464,10 +3642,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>20.611</v>
+        <v>20.476</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3476,10 +3654,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.395</v>
+        <v>2.405</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.395</v>
+        <v>2.405</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3492,10 +3670,10 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>-0.437</v>
+        <v>-0.428</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>2.64</v>
+        <v>2.619</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0</v>
@@ -3504,13 +3682,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>1.569</v>
+        <v>1.576</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>1.636</v>
+        <v>1.642</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="6">
@@ -3520,10 +3698,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.907</v>
+        <v>1.901</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>23.64</v>
+        <v>23.47</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -3532,10 +3710,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5.15</v>
+        <v>5.167</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>5.15</v>
+        <v>5.167</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -3600,13 +3778,13 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.445</v>
+        <v>1.42</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8747</v>
+        <v>0.8699</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>8.859999999999999</v>
@@ -3615,16 +3793,16 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>75.2</v>
+        <v>75</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>5.07</v>
+        <v>4.96</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.919</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="10">
@@ -3634,13 +3812,13 @@
         </is>
       </c>
       <c r="B10" s="16" t="n">
-        <v>1.301</v>
+        <v>1.241</v>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.8411</v>
+        <v>0.8293</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>9.35</v>
@@ -3649,16 +3827,16 @@
         <v>9.57</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>6.2</v>
+        <v>5.81</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3668,13 +3846,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>1.156</v>
+        <v>1.152</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8294</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -3683,16 +3861,16 @@
         <v>18.48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.579</v>
+        <v>2.132</v>
       </c>
     </row>
   </sheetData>
@@ -3767,16 +3945,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>402427.78</v>
+        <v>286349.82</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>252416.46</v>
+        <v>106099.17</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>167616.4</v>
+        <v>35966.64</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>562974.8199999999</v>
+        <v>401161.07</v>
       </c>
     </row>
     <row r="6">
@@ -3786,16 +3964,16 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>323890.01</v>
+        <v>351847.93</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>348325.82</v>
+        <v>427073.59</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>463736.55</v>
+        <v>500708.01</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>431436.49</v>
+        <v>532211.03</v>
       </c>
     </row>
     <row r="7">
@@ -3805,16 +3983,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>717305.58</v>
+        <v>827793.33</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>877838.04</v>
+        <v>1009904.95</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>426885.9</v>
+        <v>600178.34</v>
       </c>
     </row>
     <row r="8">
@@ -3824,16 +4002,16 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>1443623.37</v>
+        <v>1465991.08</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1462538.03</v>
+        <v>1568404.33</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>1509190.99</v>
+        <v>1546579.6</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>1421297.21</v>
+        <v>1533550.44</v>
       </c>
     </row>
     <row r="9">
@@ -3843,16 +4021,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>317539.23</v>
+        <v>344948.95</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>454643.68</v>
+        <v>490890.21</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>422976.95</v>
+        <v>521775.52</v>
       </c>
     </row>
     <row r="10">
@@ -3881,16 +4059,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>317539.23</v>
+        <v>344948.95</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>454643.68</v>
+        <v>490890.21</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>422976.95</v>
+        <v>521775.52</v>
       </c>
     </row>
     <row r="12">
@@ -3900,16 +4078,16 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1054547.31</v>
+        <v>1055689.39</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>998320.26</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="13">
@@ -3919,16 +4097,16 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.919</v>
+        <v>1.046</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1.073</v>
+        <v>1.265</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1.264</v>
+        <v>1.422</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.851</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="14">
@@ -3938,16 +4116,16 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>0.355</v>
+        <v>0.431</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>0.464</v>
+        <v>0.536</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.401</v>
+        <v>0.492</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.004</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="15">
@@ -3957,16 +4135,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>206968.96</v>
+        <v>234548.46</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>240658.33</v>
+        <v>290786.23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>266496.34</v>
+        <v>300159.03</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>169972.57</v>
+        <v>224390.77</v>
       </c>
     </row>
     <row r="16">
@@ -3976,16 +4154,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>919115.1800000001</v>
+        <v>886493.67</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>880383.8</v>
+        <v>858918.5</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>788050.97</v>
+        <v>755530.36</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>828347.6899999999</v>
+        <v>787384.15</v>
       </c>
     </row>
     <row r="17">
@@ -3995,7 +4173,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0</v>
@@ -4004,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4048,16 +4226,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>717305.58</v>
+        <v>827793.33</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>877838.04</v>
+        <v>1009904.95</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>426885.9</v>
+        <v>600178.34</v>
       </c>
     </row>
     <row r="22">
@@ -4086,16 +4264,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>717305.58</v>
+        <v>827793.33</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>877838.04</v>
+        <v>1009904.95</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>426885.9</v>
+        <v>600178.34</v>
       </c>
     </row>
     <row r="24">
@@ -4124,16 +4302,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>717305.58</v>
+        <v>827793.33</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>877838.04</v>
+        <v>1009904.95</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>426885.9</v>
+        <v>600178.34</v>
       </c>
     </row>
     <row r="26">
@@ -4143,16 +4321,16 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>6350.78</v>
+        <v>6898.98</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>6829.92</v>
+        <v>8373.99</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>9092.870000000001</v>
+        <v>9817.799999999999</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>8459.540000000001</v>
+        <v>10435.51</v>
       </c>
     </row>
     <row r="27">
@@ -4162,16 +4340,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>6350.78</v>
+        <v>6898.98</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>6829.92</v>
+        <v>8373.99</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9092.870000000001</v>
+        <v>9817.799999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8459.540000000001</v>
+        <v>10435.51</v>
       </c>
     </row>
     <row r="28">
@@ -4181,16 +4359,16 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>317539.23</v>
+        <v>344948.95</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>454643.68</v>
+        <v>490890.21</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>422976.95</v>
+        <v>521775.52</v>
       </c>
     </row>
     <row r="29">
@@ -4200,16 +4378,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>317539.23</v>
+        <v>344948.95</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>454643.68</v>
+        <v>490890.21</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>422976.95</v>
+        <v>521775.52</v>
       </c>
     </row>
     <row r="30">
@@ -4238,16 +4416,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>6350.78</v>
+        <v>6898.98</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6829.92</v>
+        <v>8373.99</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9092.870000000001</v>
+        <v>9817.799999999999</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8459.540000000001</v>
+        <v>10435.51</v>
       </c>
     </row>
     <row r="32">
@@ -4257,16 +4435,16 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>402427.78</v>
+        <v>286349.82</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>252416.46</v>
+        <v>106099.17</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>167616.4</v>
+        <v>35966.64</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>562974.8199999999</v>
+        <v>401161.07</v>
       </c>
     </row>
     <row r="33">
@@ -4276,16 +4454,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1054547.31</v>
+        <v>1055689.39</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>998320.26</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="34">
@@ -4348,16 +4526,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>489721.24</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>476743.58</v>
+        <v>468937.27</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>484682.15</v>
+        <v>319230.74</v>
       </c>
     </row>
     <row r="40">
@@ -4366,17 +4544,17 @@
           <t>Restricted Cash 受限现金 (PB 102%)</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
-        <v>82167.75999999999</v>
+      <c r="B40" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>89048.96000000001</v>
+        <v>99198.59</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>90710.5</v>
+        <v>192958.99</v>
       </c>
     </row>
     <row r="41">
@@ -4385,17 +4563,17 @@
           <t>Long Securities 多头证券</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>83185.75999999999</v>
+      <c r="B41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>87124.84</v>
+        <v>96238.08</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>88136.88</v>
+        <v>261745.76</v>
       </c>
     </row>
     <row r="42">
@@ -4405,16 +4583,16 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>655074.76</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>652917.38</v>
+        <v>664373.9399999999</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>663529.54</v>
+        <v>773935.49</v>
       </c>
     </row>
     <row r="43">
@@ -4423,17 +4601,17 @@
           <t>Short Securities 空头证券 (义务)</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>80556.63</v>
+      <c r="B43" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>87302.89999999999</v>
+        <v>97253.52</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>88931.87</v>
+        <v>189175.48</v>
       </c>
     </row>
     <row r="44">
@@ -4461,17 +4639,17 @@
           <t>Total Liabilities 总负债</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>80556.63</v>
+      <c r="B45" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>87302.89999999999</v>
+        <v>97253.52</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>88931.87</v>
+        <v>189175.48</v>
       </c>
     </row>
     <row r="46">
@@ -4481,16 +4659,16 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>565614.48</v>
+        <v>567120.42</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>574597.67</v>
+        <v>584760.01</v>
       </c>
     </row>
     <row r="47">
@@ -4500,16 +4678,16 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.285</v>
+        <v>0</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.308</v>
+        <v>0.341</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.308</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="48">
@@ -4519,16 +4697,16 @@
         </is>
       </c>
       <c r="B48" s="16" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="C48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="16" t="n">
-        <v>-0</v>
+        <v>-0.002</v>
       </c>
       <c r="E48" s="16" t="n">
-        <v>-0.001</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="49">
@@ -4537,17 +4715,17 @@
           <t>PM Requirement (20%)</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>32748.48</v>
+      <c r="B49" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C49" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>34885.55</v>
+        <v>38698.32</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>35413.75</v>
+        <v>90184.25</v>
       </c>
     </row>
     <row r="50">
@@ -4557,16 +4735,16 @@
         </is>
       </c>
       <c r="B50" s="12" t="n">
-        <v>541769.65</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C50" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>530728.9300000001</v>
+        <v>528422.1</v>
       </c>
       <c r="E50" s="12" t="n">
-        <v>539183.92</v>
+        <v>494575.76</v>
       </c>
     </row>
     <row r="51">
@@ -4628,17 +4806,17 @@
           <t>Long Book — Allocated Capital 分配资本</t>
         </is>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>83185.75999999999</v>
+      <c r="B55" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C55" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>87124.84</v>
+        <v>96238.08</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>88136.88</v>
+        <v>261745.76</v>
       </c>
     </row>
     <row r="56">
@@ -4666,17 +4844,17 @@
           <t>Long Book — Market Value 市值</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>83185.75999999999</v>
+      <c r="B57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>87124.84</v>
+        <v>96238.08</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>88136.88</v>
+        <v>261745.76</v>
       </c>
     </row>
     <row r="58">
@@ -4704,17 +4882,17 @@
           <t>Long Book — NAV</t>
         </is>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>83185.75999999999</v>
+      <c r="B59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>87124.84</v>
+        <v>96238.08</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>88136.88</v>
+        <v>261745.76</v>
       </c>
     </row>
     <row r="60">
@@ -4723,17 +4901,17 @@
           <t>Short Book — Allocated Capital 分配资本</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n">
-        <v>1611.13</v>
+      <c r="B60" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>1746.06</v>
+        <v>1945.07</v>
       </c>
       <c r="E60" s="12" t="n">
-        <v>1778.64</v>
+        <v>3783.51</v>
       </c>
     </row>
     <row r="61">
@@ -4742,17 +4920,17 @@
           <t>Short Book — Collateral 担保金</t>
         </is>
       </c>
-      <c r="B61" s="4" t="n">
-        <v>1611.13</v>
+      <c r="B61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C61" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>1746.06</v>
+        <v>1945.07</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1778.64</v>
+        <v>3783.51</v>
       </c>
     </row>
     <row r="62">
@@ -4761,17 +4939,17 @@
           <t>Short Book — Short Proceeds 做空收入</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n">
-        <v>80556.63</v>
+      <c r="B62" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="C62" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>87302.89999999999</v>
+        <v>97253.52</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>88931.87</v>
+        <v>189175.48</v>
       </c>
     </row>
     <row r="63">
@@ -4780,17 +4958,17 @@
           <t>Short Book — Market Value 市值(负债)</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>80556.63</v>
+      <c r="B63" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C63" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>87302.89999999999</v>
+        <v>97253.52</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>88931.87</v>
+        <v>189175.48</v>
       </c>
     </row>
     <row r="64">
@@ -4818,17 +4996,17 @@
           <t>Short Book — NAV</t>
         </is>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>1611.13</v>
+      <c r="B65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>1746.06</v>
+        <v>1945.07</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1778.64</v>
+        <v>3783.51</v>
       </c>
     </row>
     <row r="66">
@@ -4838,16 +5016,16 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>489721.24</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C66" s="12" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>476743.58</v>
+        <v>468937.27</v>
       </c>
       <c r="E66" s="12" t="n">
-        <v>484682.15</v>
+        <v>319230.74</v>
       </c>
     </row>
     <row r="67">
@@ -4857,16 +5035,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>565614.48</v>
+        <v>567120.42</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>574597.67</v>
+        <v>584760.01</v>
       </c>
     </row>
     <row r="68">
@@ -4938,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>78292.67</v>
+        <v>81930.33</v>
       </c>
     </row>
     <row r="74">
@@ -4948,16 +5126,16 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>241722.25</v>
+        <v>351847.93</v>
       </c>
       <c r="C74" s="12" t="n">
-        <v>348325.82</v>
+        <v>427073.59</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>374687.6</v>
+        <v>401509.42</v>
       </c>
       <c r="E74" s="12" t="n">
-        <v>340725.98</v>
+        <v>339252.04</v>
       </c>
     </row>
     <row r="75">
@@ -4967,16 +5145,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
-        <v>634119.8199999999</v>
+        <v>827793.33</v>
       </c>
       <c r="C75" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>790713.2</v>
+        <v>913666.87</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>338749.02</v>
+        <v>338432.58</v>
       </c>
     </row>
     <row r="76">
@@ -4986,16 +5164,16 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>875842.0699999999</v>
+        <v>1179641.26</v>
       </c>
       <c r="C76" s="12" t="n">
-        <v>1210121.57</v>
+        <v>1462305.16</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>1165400.79</v>
+        <v>1315176.29</v>
       </c>
       <c r="E76" s="12" t="n">
-        <v>757767.67</v>
+        <v>759614.95</v>
       </c>
     </row>
     <row r="77">
@@ -5005,16 +5183,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
-        <v>236982.6</v>
+        <v>344948.95</v>
       </c>
       <c r="C77" s="4" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>367340.78</v>
+        <v>393636.69</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>334045.08</v>
+        <v>332600.04</v>
       </c>
     </row>
     <row r="78">
@@ -5024,13 +5202,13 @@
         </is>
       </c>
       <c r="B78" s="12" t="n">
-        <v>87293.46000000001</v>
+        <v>284519.99</v>
       </c>
       <c r="C78" s="12" t="n">
-        <v>318453.35</v>
+        <v>460823.58</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>309127.18</v>
+        <v>432970.63</v>
       </c>
       <c r="E78" s="14" t="n">
         <v>0</v>
@@ -5043,16 +5221,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>324276.06</v>
+        <v>629468.9399999999</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>659949.25</v>
+        <v>879523.1800000001</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>676467.96</v>
+        <v>826607.3199999999</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>334045.08</v>
+        <v>332600.04</v>
       </c>
     </row>
     <row r="80">
@@ -5062,16 +5240,16 @@
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C80" s="12" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>488932.83</v>
+        <v>488568.97</v>
       </c>
       <c r="E80" s="12" t="n">
-        <v>423722.59</v>
+        <v>427014.91</v>
       </c>
     </row>
     <row r="81">
@@ -5081,16 +5259,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>1.579</v>
+        <v>2.132</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>2.187</v>
+        <v>2.495</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>2.369</v>
+        <v>2.676</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.588</v>
+        <v>1.571</v>
       </c>
     </row>
     <row r="82">
@@ -5100,16 +5278,16 @@
         </is>
       </c>
       <c r="B82" s="16" t="n">
-        <v>0.72</v>
+        <v>0.878</v>
       </c>
       <c r="C82" s="16" t="n">
-        <v>0.946</v>
+        <v>1.058</v>
       </c>
       <c r="D82" s="16" t="n">
-        <v>0.866</v>
+        <v>1.064</v>
       </c>
       <c r="E82" s="16" t="n">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="83">
@@ -5119,16 +5297,16 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>174220.48</v>
+        <v>234548.46</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>240658.33</v>
+        <v>290786.23</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>231610.8</v>
+        <v>261460.71</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>134558.82</v>
+        <v>134206.52</v>
       </c>
     </row>
     <row r="84">
@@ -5138,16 +5316,16 @@
         </is>
       </c>
       <c r="B84" s="12" t="n">
-        <v>377345.53</v>
+        <v>315623.86</v>
       </c>
       <c r="C84" s="12" t="n">
-        <v>309513.99</v>
+        <v>291995.75</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>257322.03</v>
+        <v>227108.26</v>
       </c>
       <c r="E84" s="12" t="n">
-        <v>289163.77</v>
+        <v>292808.39</v>
       </c>
     </row>
     <row r="85">
@@ -5160,13 +5338,13 @@
         <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="7" t="n">
         <v>-0</v>
-      </c>
-      <c r="D85" s="7" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E85" s="7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5210,16 +5388,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>488932.83</v>
+        <v>488568.97</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>338749.02</v>
+        <v>338432.58</v>
       </c>
     </row>
     <row r="90">
@@ -5248,16 +5426,16 @@
         </is>
       </c>
       <c r="B91" s="4" t="n">
-        <v>634119.8199999999</v>
+        <v>827793.33</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>861795.75</v>
+        <v>1035231.57</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>790713.2</v>
+        <v>913666.87</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>338749.02</v>
+        <v>338432.58</v>
       </c>
     </row>
     <row r="92">
@@ -5267,13 +5445,13 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>82553.81</v>
+        <v>277621.01</v>
       </c>
       <c r="C92" s="12" t="n">
-        <v>311623.43</v>
+        <v>452449.59</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>301780.37</v>
+        <v>425097.9</v>
       </c>
       <c r="E92" s="14" t="n">
         <v>0</v>
@@ -5286,16 +5464,16 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>488932.83</v>
+        <v>488568.97</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>338749.02</v>
+        <v>338432.58</v>
       </c>
     </row>
     <row r="94">
@@ -5314,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="12" t="n">
-        <v>6680.9</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="95">
@@ -5333,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>6680.9</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="96">
@@ -5343,16 +5521,16 @@
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>236982.6</v>
+        <v>344948.95</v>
       </c>
       <c r="C96" s="12" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>367340.78</v>
+        <v>393636.69</v>
       </c>
       <c r="E96" s="12" t="n">
-        <v>334045.08</v>
+        <v>332600.04</v>
       </c>
     </row>
     <row r="97">
@@ -5362,16 +5540,16 @@
         </is>
       </c>
       <c r="B97" s="4" t="n">
-        <v>236982.6</v>
+        <v>344948.95</v>
       </c>
       <c r="C97" s="4" t="n">
-        <v>341495.9</v>
+        <v>418699.6</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>367340.78</v>
+        <v>393636.69</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>334045.08</v>
+        <v>332600.04</v>
       </c>
     </row>
     <row r="98">
@@ -5381,13 +5559,13 @@
         </is>
       </c>
       <c r="B98" s="12" t="n">
-        <v>4739.65</v>
+        <v>6898.98</v>
       </c>
       <c r="C98" s="12" t="n">
-        <v>6829.92</v>
+        <v>8373.99</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>7346.82</v>
+        <v>7872.73</v>
       </c>
       <c r="E98" s="14" t="n">
         <v>0</v>
@@ -5409,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>6680.9</v>
+        <v>6652</v>
       </c>
     </row>
     <row r="100">
@@ -5428,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>78292.67</v>
+        <v>81930.33</v>
       </c>
     </row>
     <row r="101">
@@ -5438,16 +5616,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>488932.83</v>
+        <v>488568.97</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>423722.59</v>
+        <v>427014.91</v>
       </c>
     </row>
     <row r="102">
@@ -5540,17 +5718,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>5042.01</v>
+      <c r="B5" s="18" t="n">
+        <v>-28662.6</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>71536.83</v>
+        <v>65352.74</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>127763.88</v>
+        <v>109267.21</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>204585.35</v>
+        <v>199543.34</v>
       </c>
     </row>
     <row r="6">
@@ -5579,7 +5757,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>30340.41</v>
+        <v>39501.84</v>
       </c>
     </row>
     <row r="9">
@@ -5623,16 +5801,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3648.32</v>
+        <v>3947.06</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>8903.65</v>
+        <v>3749.39</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>-79.54000000000001</v>
+        <v>-13890.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65186.19</v>
+        <v>61537.87</v>
       </c>
     </row>
     <row r="12">
@@ -5661,7 +5839,7 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>89.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5704,17 +5882,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>1393.69</v>
+      <c r="B17" s="18" t="n">
+        <v>-32609.66</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>62633.18</v>
+        <v>61603.35</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>127843.42</v>
+        <v>123157.41</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>139399.16</v>
+        <v>138005.47</v>
       </c>
     </row>
     <row r="18">
@@ -5724,16 +5902,16 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>11.96</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>59.79</v>
+        <v>38.98</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>194.88</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>251.12</v>
+        <v>818.48</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>1877.41</v>
+        <v>6080.15</v>
       </c>
     </row>
     <row r="19">
@@ -5743,7 +5921,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>30250.79</v>
+        <v>39501.84</v>
       </c>
     </row>
     <row r="21">
@@ -5825,13 +6003,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1121042.13</v>
+        <v>1149704.73</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1054547.31</v>
+        <v>1055689.39</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>998320.26</v>
+        <v>1011774.92</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -5843,17 +6021,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>5042.01</v>
+      <c r="B6" s="19" t="n">
+        <v>-28662.6</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>71536.83</v>
+        <v>65352.74</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>127763.88</v>
+        <v>109267.21</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>204585.35</v>
+        <v>199543.34</v>
       </c>
     </row>
     <row r="7">
@@ -5901,16 +6079,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
     </row>
     <row r="10">
@@ -5919,17 +6097,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="D10" s="19" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>22.2</v>
+      <c r="B10" s="20" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>21.65</v>
       </c>
     </row>
     <row r="11">
@@ -5938,16 +6116,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="21" t="n">
+      <c r="B11" s="22" t="n">
         <v>-2.49</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="C11" s="22" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="D11" s="22" t="n">
         <v>-9.41</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>-9.470000000000001</v>
       </c>
     </row>
@@ -5992,13 +6170,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>570869.8100000001</v>
+        <v>566922.75</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>565614.48</v>
+        <v>567120.42</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>574597.67</v>
+        <v>584760.01</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6011,16 +6189,16 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>3648.32</v>
+        <v>3947.06</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>8903.65</v>
-      </c>
-      <c r="D16" s="22" t="n">
-        <v>-79.54000000000001</v>
+        <v>3749.39</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>-13890.2</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>65186.19</v>
+        <v>61537.87</v>
       </c>
     </row>
     <row r="17">
@@ -6068,16 +6246,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>574518.13</v>
+        <v>570869.8100000001</v>
       </c>
     </row>
     <row r="20">
@@ -6086,17 +6264,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="D20" s="23" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <v>12.8</v>
+      <c r="B20" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="E20" s="21" t="n">
+        <v>12.08</v>
       </c>
     </row>
     <row r="21">
@@ -6105,16 +6283,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>-2.79</v>
-      </c>
-      <c r="E21" s="21" t="n">
+      <c r="B21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="E21" s="22" t="n">
         <v>-9.57</v>
       </c>
     </row>
@@ -6159,13 +6337,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>550172.3199999999</v>
+        <v>582781.98</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>488932.83</v>
+        <v>488568.97</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>423722.59</v>
+        <v>427014.91</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6177,17 +6355,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>1393.69</v>
+      <c r="B26" s="19" t="n">
+        <v>-32609.66</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>62633.18</v>
+        <v>61603.35</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>127843.42</v>
+        <v>123157.41</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>139399.16</v>
+        <v>138005.47</v>
       </c>
     </row>
     <row r="27">
@@ -6235,16 +6413,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
     </row>
     <row r="30">
@@ -6253,17 +6431,17 @@
           <t>Return (%)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C30" s="19" t="n">
-        <v>12.81</v>
-      </c>
-      <c r="D30" s="19" t="n">
-        <v>30.17</v>
-      </c>
-      <c r="E30" s="19" t="n">
-        <v>33.82</v>
+      <c r="B30" s="20" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>33.48</v>
       </c>
     </row>
     <row r="31">
@@ -6272,16 +6450,16 @@
           <t>Max drawdown (%)</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="21" t="n">
+      <c r="B31" s="22" t="n">
         <v>-5.6</v>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="C31" s="22" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="D31" s="22" t="n">
         <v>-18.48</v>
       </c>
-      <c r="E31" s="21" t="n">
+      <c r="E31" s="22" t="n">
         <v>-18.48</v>
       </c>
     </row>
@@ -6332,7 +6510,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>71536.83</v>
+        <v>65352.74</v>
       </c>
     </row>
     <row r="5">
@@ -6342,7 +6520,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>23428.01</v>
+        <v>36170.36</v>
       </c>
     </row>
     <row r="6">
@@ -6351,7 +6529,7 @@
           <t>Financing cash flow</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6362,7 +6540,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>94964.84</v>
+        <v>101523.1</v>
       </c>
     </row>
     <row r="8">
@@ -6372,7 +6550,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>167616.4</v>
+        <v>35966.64</v>
       </c>
     </row>
     <row r="9">
@@ -6382,7 +6560,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>402427.78</v>
+        <v>286349.82</v>
       </c>
     </row>
     <row r="11">
@@ -6406,7 +6584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7990,16 +8168,6 @@
       </c>
       <c r="B159" s="12" t="n">
         <v>1121042.13</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B160" s="4" t="n">
-        <v>1126084.14</v>
       </c>
     </row>
   </sheetData>
@@ -8104,34 +8272,34 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1126084.14</v>
+        <v>1121042.13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>717305.58</v>
+        <v>827793.33</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>317539.23</v>
+        <v>344948.95</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1034844.81</v>
+        <v>1172742.28</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>399766.35</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>45.95</v>
+        <v>482844.38</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.046</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>104.61</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>52.31</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -8141,34 +8309,34 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>574518.13</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>83185.75999999999</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>80556.63</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>163742.39</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>2629.13</v>
+        <v>570869.8100000001</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.285</v>
+        <v>0</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>14.25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8178,34 +8346,34 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>551566.01</v>
+        <v>550172.3199999999</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>634119.8199999999</v>
+        <v>827793.33</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>236982.6</v>
+        <v>344948.95</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>871102.42</v>
+        <v>1172742.28</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>397137.22</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>78.97</v>
+        <v>482844.38</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.132</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>213.16</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>106.58</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8222,7 +8390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8243,7 +8411,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1751  ·  effective N pairs=5.7  ·  max pair=24.63% of gross</t>
+          <t>HHI=0.1493  ·  effective N pairs=6.7  ·  max pair=21.32% of gross</t>
         </is>
       </c>
     </row>
@@ -8282,42 +8450,42 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>183212.28</v>
+        <v>270556.2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>183212.28</v>
-      </c>
-      <c r="D6" s="20" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>17.7</v>
+        <v>270556.2</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>24.13</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>23.07</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>159949.1</v>
+        <v>175583.07</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>159949.1</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>15.46</v>
+        <v>175583.07</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>14.97</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>1</v>
@@ -8326,42 +8494,42 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>104270.18</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>104270.18</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>9.26</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>10.08</v>
+        <v>123801.64</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>-123801.64</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>10.56</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>100654.42</v>
+        <v>105875.94</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>100654.42</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>9.73</v>
+        <v>105875.94</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>9.029999999999999</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>1</v>
@@ -8370,20 +8538,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>86033.84</v>
+        <v>99282.52</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>86033.84</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>8.31</v>
+        <v>99282.52</v>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>8.470000000000001</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>1</v>
@@ -8392,20 +8560,20 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>83185.75999999999</v>
+        <v>91258.28</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>83185.75999999999</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>8.039999999999999</v>
+        <v>91258.28</v>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>7.78</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -8414,20 +8582,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>80556.63</v>
-      </c>
-      <c r="C12" s="28" t="n">
-        <v>-80556.63</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>7.78</v>
+        <v>85237.32000000001</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>85237.32000000001</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>7.27</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>1</v>
@@ -8436,20 +8604,20 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>71643.42</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>-71643.42</v>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>6.92</v>
+        <v>52669.82</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>-52669.82</v>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>4.49</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
@@ -8458,20 +8626,20 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>52191.35</v>
-      </c>
-      <c r="C14" s="28" t="n">
-        <v>-52191.35</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="E14" s="20" t="n">
-        <v>5.04</v>
+        <v>52590.2</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>-52590.2</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>4.48</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -8480,27 +8648,27 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>50571.08</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>-50571.08</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>4.89</v>
+        <v>52179.5</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>-52179.5</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>4.45</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>SECTOR NET EXPOSURE</t>
         </is>
@@ -8540,35 +8708,35 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>443815.8</v>
+        <v>545421.79</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>48594.36</v>
+        <v>102238.82</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>395221.44</v>
+        <v>443182.97</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>38.19</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>realestate</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>83185.75999999999</v>
+        <v>191113.26</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>83185.75999999999</v>
+        <v>191113.26</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>8.039999999999999</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="22">
@@ -8581,13 +8749,13 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>64553.47</v>
-      </c>
-      <c r="D22" s="28" t="n">
-        <v>-64553.47</v>
+        <v>66728.99000000001</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>-66728.99000000001</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-6.24</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="23">
@@ -8600,51 +8768,32 @@
         <v>0</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>52191.35</v>
-      </c>
-      <c r="D23" s="29" t="n">
-        <v>-52191.35</v>
+        <v>52179.5</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>-52179.5</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>-5.04</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>104270.18</v>
+        <v>91258.28</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>80556.63</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>23713.55</v>
+        <v>123801.64</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>-32543.36</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n">
-        <v>86033.84</v>
-      </c>
-      <c r="C25" s="12" t="n">
-        <v>71643.42</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>14390.42</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>1.39</v>
+        <v>-2.77</v>
       </c>
     </row>
   </sheetData>
@@ -8661,7 +8810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8681,8 +8830,8 @@
           <t>Net market beta (target≈0)</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>1.022</v>
+      <c r="B3" s="5" t="n">
+        <v>1.321</v>
       </c>
     </row>
     <row r="4">
@@ -8691,8 +8840,8 @@
           <t>Gross beta</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>1.526</v>
+      <c r="B4" s="5" t="n">
+        <v>1.877</v>
       </c>
     </row>
     <row r="5">
@@ -8701,8 +8850,8 @@
           <t>Momentum factor net (% NAV)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>35.27</v>
+      <c r="B5" s="5" t="n">
+        <v>43.07</v>
       </c>
     </row>
     <row r="6">
@@ -8718,7 +8867,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>SECTOR NET VECTOR (% of gross)</t>
         </is>
@@ -8742,18 +8891,18 @@
           <t>tech</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n">
-        <v>38.19</v>
+      <c r="B10" s="23" t="n">
+        <v>37.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>realestate</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>8.039999999999999</v>
+          <t>materials</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="12">
@@ -8762,8 +8911,8 @@
           <t>health</t>
         </is>
       </c>
-      <c r="B12" s="21" t="n">
-        <v>-6.24</v>
+      <c r="B12" s="22" t="n">
+        <v>-5.69</v>
       </c>
     </row>
     <row r="13">
@@ -8772,28 +8921,18 @@
           <t>utilities</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>-5.04</v>
+      <c r="B13" s="20" t="n">
+        <v>-4.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>materials</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
-        <v>1.39</v>
+      <c r="B14" s="22" t="n">
+        <v>-2.77</v>
       </c>
     </row>
   </sheetData>
